--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:25</t>
+    <t xml:space="preserve">2026-09-10 01:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:40</t>
+    <t xml:space="preserve">2026-09-18 11:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:36</t>
+    <t xml:space="preserve">2026-09-23 15:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
-    <t xml:space="preserve">Paiguano</t>
+    <t xml:space="preserve">Paihuano</t>
   </si>
   <si>
     <t xml:space="preserve">Vicuña</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:41</t>
+    <t xml:space="preserve">2026-10-04 10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:49</t>
+    <t xml:space="preserve">2026-10-05 16:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
